--- a/artfynd/A 5611-2023 artfynd.xlsx
+++ b/artfynd/A 5611-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117658537</v>
+        <v>117658538</v>
       </c>
       <c r="B2" t="n">
         <v>57287</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419685</v>
+        <v>419472</v>
       </c>
       <c r="R2" t="n">
-        <v>7044655</v>
+        <v>7044666</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre på 3 granar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117658539</v>
+        <v>117658540</v>
       </c>
       <c r="B3" t="n">
         <v>57287</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419429</v>
+        <v>419749</v>
       </c>
       <c r="R3" t="n">
-        <v>7044691</v>
+        <v>7044854</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117658540</v>
+        <v>117658537</v>
       </c>
       <c r="B4" t="n">
         <v>57287</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419749</v>
+        <v>419685</v>
       </c>
       <c r="R4" t="n">
-        <v>7044854</v>
+        <v>7044655</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117658538</v>
+        <v>117658539</v>
       </c>
       <c r="B5" t="n">
         <v>57287</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419472</v>
+        <v>419429</v>
       </c>
       <c r="R5" t="n">
-        <v>7044666</v>
+        <v>7044691</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre på 3 granar</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 5611-2023 artfynd.xlsx
+++ b/artfynd/A 5611-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117658538</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117658540</v>
+        <v>117658537</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419749</v>
+        <v>419685</v>
       </c>
       <c r="R3" t="n">
-        <v>7044854</v>
+        <v>7044655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117658537</v>
+        <v>117658539</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419685</v>
+        <v>419429</v>
       </c>
       <c r="R4" t="n">
-        <v>7044655</v>
+        <v>7044691</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117658539</v>
+        <v>117658540</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419429</v>
+        <v>419749</v>
       </c>
       <c r="R5" t="n">
-        <v>7044691</v>
+        <v>7044854</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
